--- a/Hoadon/HDVao/12/HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HDVao/12/HDDienTuDaCapMa.xlsx
@@ -314,6 +314,834 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>C25THT</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>16198</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>3500405761</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN HỒNG THANH</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Số 98-100-102-104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh Việt Nam</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>3827907.0</v>
+      </c>
+      <c r="L7" s="13" t="n">
+        <v>306233.0</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13" t="n">
+        <v>4134140.0</v>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>C25THT</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>16244</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>3500405761</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN HỒNG THANH</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Số 98-100-102-104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh Việt Nam</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>908333.0</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>72667.0</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13" t="n">
+        <v>981000.0</v>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>C25TMH</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>49992</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>3500442139</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH TÂM</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Số 58/29/42 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="n">
+        <v>6983264.0</v>
+      </c>
+      <c r="L9" s="13" t="n">
+        <v>558661.0</v>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>1173536.0</v>
+      </c>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13" t="n">
+        <v>7541925.0</v>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>C25TDL</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>107908</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>3501970854</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>3.1054445E7</v>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>2484356.0</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>1886837.0</v>
+      </c>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13" t="n">
+        <v>3.3538801E7</v>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>C25TMG</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>19464</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>3502243033</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH GIA</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Số 58/29/40 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>7592593.0</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>607407.0</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13" t="n">
+        <v>8200000.0</v>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S11" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>C25TMH</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>8750</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>3502426816</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>6206399.0</v>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>496512.0</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13" t="n">
+        <v>6702911.0</v>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>C25TYY</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>1128</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>3502478885</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ LINH CHÂU VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Số 43 Đường Nguyễn Quyền, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>1.2037037E8</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>9629630.0</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13" t="n">
+        <v>1.3E8</v>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>C25TMQ</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>3502548074</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH PHÂN PHỐI MINH VÀ QUÂN</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>472 Nguyễn An Ninh, phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="n">
+        <v>3005370.0</v>
+      </c>
+      <c r="L14" s="13" t="n">
+        <v>240430.0</v>
+      </c>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13" t="n">
+        <v>3245800.0</v>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>869</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>3502548116</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐỨC DẬT</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>15 Cao Bá Quát, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>1.1587963E7</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>927037.0</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13" t="n">
+        <v>1.2515E7</v>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>C25THB</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>3502552641</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HB COFFEE</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>24 Huỳnh Văn Hớn, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>2657400.0</v>
+      </c>
+      <c r="L16" s="13" t="n">
+        <v>212592.0</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13" t="n">
+        <v>2869992.0</v>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:S3"/>

--- a/Hoadon/HDVao/12/HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HDVao/12/HDDienTuDaCapMa.xlsx
@@ -325,32 +325,32 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25THT</t>
+          <t>C25TLH</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>16198</t>
+          <t>15460</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>3500405761</t>
+          <t>1101963538</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN HỒNG THANH</t>
+          <t>CÔNG TY CỔ PHẦN CAO LỢI HƯNG VIỆT NAM</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Số 98-100-102-104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh Việt Nam</t>
+          <t>Ấp Thuận Hòa 2, Xã Hòa Khánh, Tỉnh Tây Ninh, Việt Nam</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -364,17 +364,17 @@
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>3827907.0</v>
+        <v>3900000.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>306233.0</v>
+        <v>312000.0</v>
       </c>
       <c r="M7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>4134140.0</v>
+        <v>4212000.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -413,7 +413,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>16244</t>
+          <t>16198</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -447,17 +447,17 @@
         </is>
       </c>
       <c r="K8" s="13" t="n">
-        <v>908333.0</v>
+        <v>3827907.0</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>72667.0</v>
+        <v>306233.0</v>
       </c>
       <c r="M8" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>981000.0</v>
+        <v>4134140.0</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -491,12 +491,12 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25TMH</t>
+          <t>C25THT</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>49992</t>
+          <t>16244</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -506,17 +506,17 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>3500442139</t>
+          <t>3500405761</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH TÂM</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN HỒNG THANH</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Số 58/29/42 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 98-100-102-104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh Việt Nam</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
@@ -530,17 +530,17 @@
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>6983264.0</v>
+        <v>908333.0</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>558661.0</v>
+        <v>72667.0</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>1173536.0</v>
+        <v>0.0</v>
       </c>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="n">
-        <v>7541925.0</v>
+        <v>981000.0</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -574,32 +574,32 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25TDL</t>
+          <t>C25THT</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>107908</t>
+          <t>16289</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>3501970854</t>
+          <t>3500405761</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN HỒNG THANH</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 98-100-102-104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh Việt Nam</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
@@ -613,17 +613,17 @@
         </is>
       </c>
       <c r="K10" s="13" t="n">
-        <v>3.1054445E7</v>
+        <v>2963224.0</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>2484356.0</v>
+        <v>237058.0</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>1886837.0</v>
+        <v>0.0</v>
       </c>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="n">
-        <v>3.3538801E7</v>
+        <v>3200282.0</v>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
@@ -657,32 +657,32 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C25TMG</t>
+          <t>C25THT</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>19464</t>
+          <t>16291</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>3502243033</t>
+          <t>3500405761</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH GIA</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN HỒNG THANH</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Số 58/29/40 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 98-100-102-104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh Việt Nam</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
@@ -696,17 +696,17 @@
         </is>
       </c>
       <c r="K11" s="13" t="n">
-        <v>7592593.0</v>
+        <v>3947963.0</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>607407.0</v>
+        <v>315837.0</v>
       </c>
       <c r="M11" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="n">
-        <v>8200000.0</v>
+        <v>4263800.0</v>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
@@ -740,32 +740,32 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C25TMH</t>
+          <t>C25THT</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>8750</t>
+          <t>16292</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>3502426816</t>
+          <t>3500405761</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN HỒNG THANH</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 98-100-102-104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh Việt Nam</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
@@ -779,17 +779,17 @@
         </is>
       </c>
       <c r="K12" s="13" t="n">
-        <v>6206399.0</v>
+        <v>1.0138889E7</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>496512.0</v>
+        <v>811111.0</v>
       </c>
       <c r="M12" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="n">
-        <v>6702911.0</v>
+        <v>1.095E7</v>
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
@@ -823,32 +823,32 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>C25TYY</t>
+          <t>C25THT</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>16300</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>3502478885</t>
+          <t>3500405761</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ LINH CHÂU VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN HỒNG THANH</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Số 43 Đường Nguyễn Quyền, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 98-100-102-104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh Việt Nam</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
@@ -862,17 +862,17 @@
         </is>
       </c>
       <c r="K13" s="13" t="n">
-        <v>1.2037037E8</v>
+        <v>5930556.0</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>9629630.0</v>
+        <v>474444.0</v>
       </c>
       <c r="M13" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N13" s="13"/>
       <c r="O13" s="13" t="n">
-        <v>1.3E8</v>
+        <v>6405000.0</v>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
@@ -906,12 +906,12 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>C25TMQ</t>
+          <t>C25TMH</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>49992</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -921,17 +921,17 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>3502548074</t>
+          <t>3500442139</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH PHÂN PHỐI MINH VÀ QUÂN</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH TÂM</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>472 Nguyễn An Ninh, phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/29/42 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
@@ -945,15 +945,17 @@
         </is>
       </c>
       <c r="K14" s="13" t="n">
-        <v>3005370.0</v>
+        <v>6983264.0</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>240430.0</v>
-      </c>
-      <c r="M14" s="13"/>
+        <v>558661.0</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>1173536.0</v>
+      </c>
       <c r="N14" s="13"/>
       <c r="O14" s="13" t="n">
-        <v>3245800.0</v>
+        <v>7541925.0</v>
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
@@ -987,12 +989,12 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>C25TDD</t>
+          <t>C25TDL</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>107908</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -1002,17 +1004,17 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>3502548116</t>
+          <t>3501970854</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐỨC DẬT</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>15 Cao Bá Quát, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
@@ -1026,17 +1028,17 @@
         </is>
       </c>
       <c r="K15" s="13" t="n">
-        <v>1.1587963E7</v>
+        <v>3.1054445E7</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>927037.0</v>
+        <v>2484356.0</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>0.0</v>
+        <v>1886837.0</v>
       </c>
       <c r="N15" s="13"/>
       <c r="O15" s="13" t="n">
-        <v>1.2515E7</v>
+        <v>3.3538801E7</v>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
@@ -1070,32 +1072,32 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>C25THB</t>
+          <t>C25TDL</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>108169</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>3502552641</t>
+          <t>3501970854</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HB COFFEE</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>24 Huỳnh Văn Hớn, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 58/23C Nguyễn Gia Thiều, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
@@ -1109,34 +1111,1028 @@
         </is>
       </c>
       <c r="K16" s="13" t="n">
-        <v>2657400.0</v>
+        <v>8696807.0</v>
       </c>
       <c r="L16" s="13" t="n">
-        <v>212592.0</v>
+        <v>695743.0</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>0.0</v>
+        <v>242113.0</v>
       </c>
       <c r="N16" s="13"/>
       <c r="O16" s="13" t="n">
+        <v>9392550.0</v>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>C25TPQ</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>3502236614</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>DOANH NGHIỆP TƯ NHÂN QUỐC ĐẠI - PHÚ QUÝ</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Số 140/8/5A Lưu Chí Hiếu, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>1.1299074E7</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>903926.0</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13" t="n">
+        <v>1.2203E7</v>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>C25TMG</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>19464</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>3502243033</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH GIA</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Số 58/29/40 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="n">
+        <v>7592593.0</v>
+      </c>
+      <c r="L18" s="13" t="n">
+        <v>607407.0</v>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13" t="n">
+        <v>8200000.0</v>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>C25THP</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>3064</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>3502343006</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI MAI LINH PHÁT</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>11 Hà Huy Tập, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>2997825.0</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>239826.0</v>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>529027.0</v>
+      </c>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13" t="n">
+        <v>3237651.0</v>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>C25THP</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>3065</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>3502343006</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI MAI LINH PHÁT</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>11 Hà Huy Tập, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="n">
+        <v>8651269.0</v>
+      </c>
+      <c r="L20" s="13" t="n">
+        <v>692101.0</v>
+      </c>
+      <c r="M20" s="13" t="n">
+        <v>1526688.0</v>
+      </c>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13" t="n">
+        <v>9343370.0</v>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>C25THP</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>3066</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>3502343006</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI MAI LINH PHÁT</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>11 Hà Huy Tập, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>2267533.0</v>
+      </c>
+      <c r="L21" s="13" t="n">
+        <v>181403.0</v>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>369143.0</v>
+      </c>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13" t="n">
+        <v>2448936.0</v>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>C25TMH</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>8750</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>3502426816</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Số 104 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="n">
+        <v>6206399.0</v>
+      </c>
+      <c r="L22" s="13" t="n">
+        <v>496512.0</v>
+      </c>
+      <c r="M22" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13" t="n">
+        <v>6702911.0</v>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>C25TTL</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>10473</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>3502459466</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THUỐC LÁ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>39 Nguyễn Bỉnh Khiêm, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>2.2272727E7</v>
+      </c>
+      <c r="L23" s="13" t="n">
+        <v>2227273.0</v>
+      </c>
+      <c r="M23" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13" t="n">
+        <v>2.45E7</v>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>C25TYY</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>1128</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>3502478885</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ LINH CHÂU VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Số 43 Đường Nguyễn Quyền, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="n">
+        <v>1.2037037E8</v>
+      </c>
+      <c r="L24" s="13" t="n">
+        <v>9629630.0</v>
+      </c>
+      <c r="M24" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13" t="n">
+        <v>1.3E8</v>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q24" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>C25TMQ</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>3502548074</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH PHÂN PHỐI MINH VÀ QUÂN</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>472 Nguyễn An Ninh, phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="n">
+        <v>3005370.0</v>
+      </c>
+      <c r="L25" s="13" t="n">
+        <v>240430.0</v>
+      </c>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13"/>
+      <c r="O25" s="13" t="n">
+        <v>3245800.0</v>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>C25TDD</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>869</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>3502548116</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐỨC DẬT</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>15 Cao Bá Quát, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="n">
+        <v>1.1587963E7</v>
+      </c>
+      <c r="L26" s="13" t="n">
+        <v>927037.0</v>
+      </c>
+      <c r="M26" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13" t="n">
+        <v>1.2515E7</v>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q26" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>C25THP</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>6015</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>02/12/2025</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>3502550066</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="n">
+        <v>1.0730424E7</v>
+      </c>
+      <c r="L27" s="13" t="n">
+        <v>858434.0</v>
+      </c>
+      <c r="M27" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13" t="n">
+        <v>1.1588858E7</v>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>C25THB</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>3502552641</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HB COFFEE</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>24 Huỳnh Văn Hớn, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="n">
+        <v>2657400.0</v>
+      </c>
+      <c r="L28" s="13" t="n">
+        <v>212592.0</v>
+      </c>
+      <c r="M28" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13" t="n">
         <v>2869992.0</v>
       </c>
-      <c r="P16" s="7" t="inlineStr">
+      <c r="P28" s="7" t="inlineStr">
         <is>
           <t>VND</t>
         </is>
       </c>
-      <c r="Q16" s="7" t="inlineStr">
+      <c r="Q28" s="7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="R28" s="6" t="inlineStr">
         <is>
           <t>Hóa đơn mới</t>
         </is>
       </c>
-      <c r="S16" s="6" t="inlineStr">
+      <c r="S28" s="6" t="inlineStr">
         <is>
           <t>Đã cấp mã hóa đơn</t>
         </is>

--- a/Hoadon/HDVao/12/HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HDVao/12/HDDienTuDaCapMa.xlsx
@@ -906,32 +906,32 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>C25TAA</t>
+          <t>C25TEE</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>42889</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>0110366670</t>
+          <t>0107581903-001</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH SỞ HỮU TRÍ TUỆ TAGA</t>
+          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Số 12 Ngõ 203 đường Hữu Hưng, Phường Tây Mỗ, Thành phố Hà Nội, Việt Nam</t>
+          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
@@ -945,17 +945,17 @@
         </is>
       </c>
       <c r="K14" s="13" t="n">
-        <v>6000000.0</v>
+        <v>3740741.0</v>
       </c>
       <c r="L14" s="13" t="n">
+        <v>299259.0</v>
+      </c>
+      <c r="M14" s="13" t="n">
         <v>300000.0</v>
-      </c>
-      <c r="M14" s="13" t="n">
-        <v>0.0</v>
       </c>
       <c r="N14" s="13"/>
       <c r="O14" s="13" t="n">
-        <v>6300000.0</v>
+        <v>4040000.0</v>
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
@@ -989,12 +989,12 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TAA</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>33140</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -1004,17 +1004,17 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>0110366670</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY TNHH SỞ HỮU TRÍ TUỆ TAGA</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 12 Ngõ 203 đường Hữu Hưng, Phường Tây Mỗ, Thành phố Hà Nội, Việt Nam</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
@@ -1028,15 +1028,17 @@
         </is>
       </c>
       <c r="K15" s="13" t="n">
-        <v>4032407.0</v>
+        <v>6000000.0</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>322593.0</v>
-      </c>
-      <c r="M15" s="13"/>
+        <v>300000.0</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N15" s="13"/>
       <c r="O15" s="13" t="n">
-        <v>4355000.0</v>
+        <v>6300000.0</v>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
@@ -1075,7 +1077,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>33141</t>
+          <t>33140</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -1156,7 +1158,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>33142</t>
+          <t>33141</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -1237,7 +1239,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>33143</t>
+          <t>33142</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -1318,7 +1320,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>33150</t>
+          <t>33143</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -1399,12 +1401,12 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>33327</t>
+          <t>33150</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -1475,32 +1477,32 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>C25TPL</t>
+          <t>C25TAB</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>33327</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>0309414020</t>
+          <t>0302263527</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ XÂY DỰNG PHAN LÊ</t>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>A-107 Khu nhà ở và nghỉ ngơi giải trí, đường số 5, Phường Tân Hưng, TP Hồ Chí Minh, Việt Nam</t>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
@@ -1514,34 +1516,684 @@
         </is>
       </c>
       <c r="K21" s="13" t="n">
-        <v>2.48909091E8</v>
+        <v>4032407.0</v>
       </c>
       <c r="L21" s="13" t="n">
-        <v>2.4890909E7</v>
-      </c>
-      <c r="M21" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>322593.0</v>
+      </c>
+      <c r="M21" s="13"/>
       <c r="N21" s="13"/>
       <c r="O21" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>33524</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="n">
+        <v>4576852.0</v>
+      </c>
+      <c r="L22" s="13" t="n">
+        <v>366148.0</v>
+      </c>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13" t="n">
+        <v>4943000.0</v>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>33567</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L23" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>33568</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L24" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q24" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>33569</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L25" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13"/>
+      <c r="O25" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>33570</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L26" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q26" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>33571</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L27" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>C25TBV</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>15434</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>0304998358-056</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH 34 - CÔNG TY CỔ PHẦN THƯƠNG MẠI - DỊCH VỤ PHONG VŨ</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>L11 G2 Đường Nguyễn Thái Học,phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="n">
+        <v>1.249074074E7</v>
+      </c>
+      <c r="L28" s="13" t="n">
+        <v>999259.26</v>
+      </c>
+      <c r="M28" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13" t="n">
+        <v>1.349E7</v>
+      </c>
+      <c r="P28" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q28" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>C25TPL</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>01/12/2025</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>0309414020</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ XÂY DỰNG PHAN LÊ</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>A-107 Khu nhà ở và nghỉ ngơi giải trí, đường số 5, Phường Tân Hưng, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="n">
+        <v>2.48909091E8</v>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>2.4890909E7</v>
+      </c>
+      <c r="M29" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13" t="n">
         <v>2.738E8</v>
       </c>
-      <c r="P21" s="7" t="inlineStr">
+      <c r="P29" s="7" t="inlineStr">
         <is>
           <t>VND</t>
         </is>
       </c>
-      <c r="Q21" s="7" t="inlineStr">
+      <c r="Q29" s="7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
+      <c r="R29" s="6" t="inlineStr">
         <is>
           <t>Hóa đơn mới</t>
         </is>
       </c>
-      <c r="S21" s="6" t="inlineStr">
+      <c r="S29" s="6" t="inlineStr">
         <is>
           <t>Đã cấp mã hóa đơn</t>
         </is>
